--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -365,7 +365,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -594,7 +594,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -682,7 +682,7 @@
     <t>Patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -725,7 +725,7 @@
     <t>Patient.identifier:nationalid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_nationalId</t>
+    <t>http://openelis-global.org/pat_nationalId</t>
   </si>
   <si>
     <t>Patient.identifier:nationalid.value</t>
@@ -758,7 +758,7 @@
     <t>Patient.identifier:subjectnumber.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_subjectNumber</t>
+    <t>http://openelis-global.org/pat_subjectNumber</t>
   </si>
   <si>
     <t>Patient.identifier:subjectnumber.value</t>
@@ -791,7 +791,7 @@
     <t>Patient.identifier:stnumber.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_stNumber</t>
+    <t>http://openelis-global.org/pat_stNumber</t>
   </si>
   <si>
     <t>Patient.identifier:stnumber.value</t>
@@ -824,7 +824,7 @@
     <t>Patient.identifier:guid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_guid</t>
+    <t>http://openelis-global.org/pat_guid</t>
   </si>
   <si>
     <t>Patient.identifier:guid.value</t>
@@ -857,7 +857,7 @@
     <t>Patient.identifier:uuid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_uuid</t>
+    <t>http://openelis-global.org/pat_uuid</t>
   </si>
   <si>
     <t>Patient.identifier:uuid.value</t>
@@ -1094,7 +1094,7 @@
     <t>The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -1226,7 +1226,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -1411,7 +1411,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1482,7 +1482,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1815,7 +1815,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="42.9296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="56.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1830,7 +1830,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:58:07+00:00</t>
+    <t>2026-05-12T16:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
